--- a/Documentation/Dictionary.xlsx
+++ b/Documentation/Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/562f170528f46325/My Documents/GitHub/ge-smarttemp/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{41BC8FF7-AB83-E74E-8837-E1FCC09A0C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41AB1A3A-5555-5848-BD52-1DDB7A3F100D}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{41BC8FF7-AB83-E74E-8837-E1FCC09A0C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2385CB01-0BF6-FF42-9977-3DA07B93478F}"/>
   <bookViews>
-    <workbookView xWindow="9540" yWindow="6440" windowWidth="28800" windowHeight="16280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3560" yWindow="6400" windowWidth="28800" windowHeight="16280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All working. Can we regenerate " sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
   <si>
     <t>Field</t>
   </si>
@@ -97,20 +97,56 @@
     <t>Array of integers for all zones</t>
   </si>
   <si>
-    <t>Home Assitant Entity</t>
-  </si>
-  <si>
     <t>dis_room_humi</t>
   </si>
   <si>
     <t>Zone Humidity</t>
+  </si>
+  <si>
+    <t>Home Assistant Entity</t>
+  </si>
+  <si>
+    <t>dis_room_temp</t>
+  </si>
+  <si>
+    <t>fan_mode</t>
+  </si>
+  <si>
+    <t>fan_status</t>
+  </si>
+  <si>
+    <t>zoneX_name</t>
+  </si>
+  <si>
+    <t>mac</t>
+  </si>
+  <si>
+    <t>MAC Address</t>
+  </si>
+  <si>
+    <t>Zone Name</t>
+  </si>
+  <si>
+    <t>Auto/Continious</t>
+  </si>
+  <si>
+    <t>Zone Temperature</t>
+  </si>
+  <si>
+    <t>0: Auto, 1: Continious</t>
+  </si>
+  <si>
+    <t>autoofftime</t>
+  </si>
+  <si>
+    <t>Done</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -120,6 +156,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -153,9 +196,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -375,7 +419,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="3" width="38.5" customWidth="1"/>
@@ -393,7 +437,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -485,14 +529,73 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/Dictionary.xlsx
+++ b/Documentation/Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/562f170528f46325/My Documents/GitHub/ge-smarttemp/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="220" documentId="8_{41BC8FF7-AB83-E74E-8837-E1FCC09A0C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE684163-11BD-D449-9B74-99FCCC20922E}"/>
+  <xr:revisionPtr revIDLastSave="223" documentId="8_{41BC8FF7-AB83-E74E-8837-E1FCC09A0C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4571A8D2-673C-594A-86B9-DBD34C81A19A}"/>
   <bookViews>
-    <workbookView xWindow="3920" yWindow="10800" windowWidth="28780" windowHeight="16280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26800" yWindow="2480" windowWidth="28800" windowHeight="16300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dictionary" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
     </textPr>
   </connection>
   <connection id="2" xr16:uid="{C561AA97-0CB1-CE4B-B8A1-CEF82942D0E5}" name="Lounge.pair_key" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" sourceFile="/Users/robert/Library/CloudStorage/OneDrive-Personal/Desktop/Lounge.pair_key.json">
+    <textPr sourceFile="/Users/robert/Library/CloudStorage/OneDrive-Personal/Desktop/Lounge.pair_key.json">
       <textFields count="4">
         <textField/>
         <textField/>
@@ -675,6 +675,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1360,7 +1364,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E9865F-8FFC-D44B-8B68-BB05D4233726}">
-  <dimension ref="A1:F174"/>
+  <dimension ref="A1:I180"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1.6640625" bestFit="1" customWidth="1"/>
@@ -1369,6 +1373,7 @@
     <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="2.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
@@ -2662,6 +2667,22 @@
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A174" t="s">
         <v>111</v>
+      </c>
+    </row>
+    <row r="178" spans="9:9" x14ac:dyDescent="0.15">
+      <c r="I178">
+        <v>1767619818</v>
+      </c>
+    </row>
+    <row r="179" spans="9:9" x14ac:dyDescent="0.15">
+      <c r="I179">
+        <v>1767616218</v>
+      </c>
+    </row>
+    <row r="180" spans="9:9" x14ac:dyDescent="0.15">
+      <c r="I180">
+        <f>I179-I178</f>
+        <v>-3600</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/Dictionary.xlsx
+++ b/Documentation/Dictionary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/562f170528f46325/My Documents/GitHub/ge-smarttemp/Documentation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/562f170528f46325/My Documents/GitHub/ha-smarttemp/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="223" documentId="8_{41BC8FF7-AB83-E74E-8837-E1FCC09A0C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4571A8D2-673C-594A-86B9-DBD34C81A19A}"/>
   <bookViews>
-    <workbookView xWindow="26800" yWindow="2480" windowWidth="28800" windowHeight="16300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34780" yWindow="18140" windowWidth="28800" windowHeight="16300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dictionary" sheetId="1" r:id="rId1"/>
